--- a/images/unitpic/Claude outputs/missing_image_folders.xlsx
+++ b/images/unitpic/Claude outputs/missing_image_folders.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing'!$A$1:$AE$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing'!$A$1:$AD$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE37"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,31 +436,30 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="51" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="60" customWidth="1" min="21" max="21"/>
     <col width="60" customWidth="1" min="22" max="22"/>
-    <col width="42" customWidth="1" min="23" max="23"/>
+    <col width="39" customWidth="1" min="23" max="23"/>
     <col width="60" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="51" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="4" customWidth="1" min="30" max="30"/>
-    <col width="3" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,7 +1058,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>subsale</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,37 +1068,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Petaling Jaya / Damansara</t>
+          <t>Puchong</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Damansara Perdana</t>
+          <t>Taman Putra Perdana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flora Damansara</t>
+          <t>LBS Skylake Residence</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bumi Lot</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Block E Level 16 | Renovated (3 extra bedrooms added) | Fully Tenanted Room-by-Room RM2090/month | Covered Parking | Market Value RM360k (Bank) / RM380k (LPPSA)</t>
+          <t>Partially furnished (aircond in master bedroom, water heater in master bath, kitchen cabinet, sofa, TV cabinet, wet kitchen with stove, washing machine, fridge) | Facilities: pool, playground, security, gym | Low floor</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1109,7 +1108,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1119,7 +1118,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1129,22 +1128,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Partially Furnished</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Leasehold</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1159,52 +1158,47 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>MRT Mutiara Damansara | The Curve | IKEA Damansara | Empire City Shopping Mall | LDP Highway</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>/images/unitpic/floradamansaraBUFF/pic1.jpg</t>
+          <t>LRT Puchong Prima | IOI Mall Puchong | Columbia Asia Hospital Puchong | MAHSA University | LDP Highway</t>
+        </is>
+      </c>
+      <c r="V5" s="1" t="inlineStr">
+        <is>
+          <t>https://haniproperties.com/images/unitpic/lbsskylakeresidenceHF/pic1.jpg</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>floradamansaraBUFF</t>
+          <t>lbsskylakeresidenceHF</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the subsale unit at Flora Damansara, Damansara Perdana. Price: RM280000. Ref: ZYP</t>
+          <t>Hi Hani, I'm interested in the unit rental at LBS Skylake Residence, Taman Putra Perdana. Price: RM1700. Ref: HF</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>7/10/2026</t>
+          <t>2/9/2026</t>
         </is>
       </c>
       <c r="Z5" s="1" t="inlineStr">
         <is>
-          <t>https://telegram.me/zikriyussofperundinghartanah/1006</t>
+          <t>https://t.me/iqalisting/3173</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/9/2026</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>BUFF</t>
+          <t>HF</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>(B)</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1221,37 +1215,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Puchong</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taman Putra Perdana</t>
+          <t>Seksyen 14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LBS Skylake Residence</t>
+          <t>Alinea Suites</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muslim Only | Malaysian Only | Family/Couple Preferred</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Partially furnished (aircond in master bedroom, water heater in master bath, kitchen cabinet, sofa, TV cabinet, wet kitchen with stove, washing machine, fridge) | Facilities: pool, playground, security, gym | Low floor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1266,32 +1260,32 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>450</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Service Residence</t>
+          <t>Studio</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1311,37 +1305,37 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>LRT Puchong Prima | IOI Mall Puchong | Columbia Asia Hospital Puchong | MAHSA University | LDP Highway</t>
-        </is>
-      </c>
-      <c r="V6" s="1" t="inlineStr">
-        <is>
-          <t>https://haniproperties.com/images/unitpic/lbsskylakeresidenceHF/pic1.jpg</t>
+          <t>KTM Shah Alam | Plaza Alam Sentral | SACC Mall | Avisena Specialist Hospital | UiTM Shah Alam</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>/images/unitpic/alineasuitesHF/pic1.jpg</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>lbsskylakeresidenceHF</t>
+          <t>alineasuitesHF</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at LBS Skylake Residence, Taman Putra Perdana. Price: RM1700. Ref: HF</t>
+          <t>Hi Hani, I'm interested in the unit rental at Alinea Suites, Seksyen 14. Price: RM1600. Ref: HF</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2/9/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="Z6" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/iqalisting/3173</t>
+          <t>https://t.me/iqalisting/3213</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/9/2026</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1350,6 +1344,11 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1368,37 +1367,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bangi/Kajang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jalan Bukit</t>
+          <t>Dutamas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Residensi Nexus Kajang</t>
+          <t>Solaris Dutamas</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Malaysian Only</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tower A | Kitchen Cabinet | Water Heater</t>
+          <t>High Floor | Corner Unit</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1413,27 +1412,27 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>750</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1458,42 +1457,42 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>MRT-KTM Kajang Station | Plaza Metro Kajang | Hospital Kajang | New Era University College | SILK Highway</t>
+          <t>KTM Segambut | Publika Shopping Gallery | MITEC | MATRADE | DUKE Highway</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>/images/unitpic/residensinexuskajangADL2/pic1.jpg</t>
+          <t>/images/unitpic/solarisdutamasEX/pic1.jpg</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>residensinexuskajangADL2</t>
+          <t>solarisdutamasEX</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Residensi Nexus Kajang, Jalan Bukit. Price: RM1500. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at Solaris Dutamas, Dutamas. Price: RM2800. Ref: EX</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z7" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14115</t>
+          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31933</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Nov-26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1520,22 +1519,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Ampang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sungai Besi</t>
+          <t>Ampang Hilir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Midfields Condominium</t>
+          <t>Astoria Ampang</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1545,12 +1544,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Washing Machine | Refrigerator | Microwave | Oven</t>
+          <t>Level 17 | Unblocked View</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1565,12 +1564,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1580,7 +1579,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>735</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1590,7 +1589,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1610,32 +1609,32 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>LRT Salak Selatan | KTM Salak Selatan | TBS Bandar Tasik Selatan | Taman Desa Medical Centre | Sungai Besi Expressway</t>
+          <t>Ampang Park LRT/MRT Station | Great Eastern Mall | Ampang Point Shopping Centre | Gleneagles Hospital Kuala Lumpur | AKLEH Highway</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>/images/unitpic/midfieldscondominiumADL/pic1.jpg</t>
+          <t>/images/unitpic/astoriaampangEX/pic1.jpg</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>midfieldscondominiumADL</t>
+          <t>astoriaampangEX</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Midfields Condominium, Sungai Besi. Price: RM2400. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at Astoria Ampang, Ampang Hilir. Price: RM2700. Ref: EX</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z8" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14130</t>
+          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31944</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1645,7 +1644,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1672,22 +1671,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bangi/Kajang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mutiara Heights</t>
+          <t>Wangsa Maju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Residensi Topaz</t>
+          <t>Sfera Residence</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1697,12 +1696,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Level 34 | High Floor | Mountain View | East Facing | Balcony</t>
+          <t>Level 9 | Brand New Unit | Price Negotiable</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1722,7 +1721,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1732,17 +1731,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>997</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1762,42 +1761,42 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>MRT Sungai Jernih | MRT Kajang | Plaza Metro Kajang | Hospital Kajang | New Era University College</t>
+          <t>LRT Sri Rampai (~200m walk) | Wangsa Walk Mall | Melawati Mall | TAR UMT | DUKE Highway</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>/images/unitpic/residensitopazADL2/pic1.jpg</t>
+          <t>/images/unitpic/sferaresidenceEX2/pic1.jpg</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>residensitopazADL2</t>
+          <t>sferaresidenceEX2</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Residensi Topaz, Mutiara Heights. Price: RM1800. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at Sfera Residence, Wangsa Maju. Price: RM3700. Ref: EX</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z9" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14145</t>
+          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31955</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Nov-26</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1824,22 +1823,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Selayang</t>
+          <t>Bukit Jalil</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Selayang</t>
+          <t>Bukit Jalil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Magna Ville Condominium</t>
+          <t>Residensi Jalilmas</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1849,12 +1848,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Level 22 | Renovated</t>
+          <t>Level 23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1869,32 +1868,32 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>801</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1914,42 +1913,42 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Kampung Batu MRT Station | Selayang Mall | Hospital Selayang | UiTM Selayang Campus | MRR2 Highway</t>
+          <t>LRT Awan Besar | LRT Muhibbah | Pavilion Bukit Jalil | Asia Pacific University (APU) | KESAS Highway</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>/images/unitpic/magnavillecondominiumADL2/pic1.jpg</t>
+          <t>/images/unitpic/residensijalilmasEX/pic1.jpg</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>magnavillecondominiumADL2</t>
+          <t>residensijalilmasEX</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Magna Ville Condominium, Selayang. Price: RM1400. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at Residensi Jalilmas, Bukit Jalil. Price: RM1650. Ref: EX</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z10" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14166</t>
+          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31972</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7/11/2026</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>EX</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1981,17 +1980,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Puchong</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taman Putra Perdana</t>
+          <t>Jalan Sultan Ismail</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LBS Skylake Residence</t>
+          <t>Majestic Residence</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2001,12 +2000,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>End Unit | High Floor (Block A Level 24) | Balcony</t>
+          <t>High Floor | KL City View | Free Monthly Cleaning Service</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2021,27 +2020,27 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>459</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2066,42 +2065,42 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>LRT Puchong Prima | Lotus's Bukit Puchong | SMK Putra Perdana | LDP Highway | SKVE Highway</t>
+          <t>Medan Tuanku Monorail Station | Quill City Mall | SOGO Kuala Lumpur | Suria KLCC | Kampung Baru</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>/images/unitpic/lbsskylakeresidenceFPR/pic1.jpg</t>
+          <t>/images/unitpic/majesticresidenceYR/pic1.jpg</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>lbsskylakeresidenceFPR</t>
+          <t>majesticresidenceYR</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at LBS Skylake Residence, Taman Putra Perdana. Price: RM1750. Ref: FPR</t>
+          <t>Hi Hani, I'm interested in the unit rental at Majestic Residence, Jalan Sultan Ismail. Price: RM3500. Ref: YR</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z11" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/fathurpropertyrental/31153</t>
+          <t>https://t.me/yanzrealty/643</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Jan-27</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>FPR</t>
+          <t>YR</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2128,22 +2127,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bangi/Kajang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Southville City</t>
+          <t>Wangsa Maju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Savanna Executive Suites @ Southville City</t>
+          <t>Sunway Avila Residences</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2153,12 +2152,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Price Reduced (from RM2100) | Block C1, Level 29 (High floor) | Deposit: 1+1+0.5+TA</t>
+          <t>High Floor | Balcony with KLCC View</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2178,7 +2177,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2188,7 +2187,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2218,50 +2217,50 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Bangi KTM Station | IOI City Mall Putrajaya | Universiti Kebangsaan Malaysia (UKM) | Kolej Poly-Tech MARA Bangi | ELITE Highway</t>
+          <t>LRT Sri Rampai (walking distance) | Wangsa Walk Mall | Setapak Central Mall | TAR UMT | DUKE Highway</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>/images/unitpic/savannaexecutivesuitessouthvillecityFPR3/pic1.jpg</t>
+          <t>/images/unitpic/sunwayavilaresidencesEX/pic1.jpg</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>savannaexecutivesuitessouthvillecityFPR3</t>
+          <t>sunwayavilaresidencesEX</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Savanna Executive Suites @ Southville City, Southville City. Price: RM1800. Ref: FPR</t>
+          <t>Hi Hani, I'm interested in the unit rental at Sunway Avila Residences, Wangsa Maju. Price: RM3500. Ref: EX</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z12" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/fathurpropertyrental/27348</t>
+          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/32024</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Immediate</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>FPR</t>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2280,22 +2279,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Bangi/Kajang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Taman Tun Perak</t>
+          <t>Sungai Tangkas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pangsapuri Waja</t>
+          <t>Apartment Taman Tropika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2305,12 +2304,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>950</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Level 3 (Walk-Up) | Facing Playground | Deposit: 2+1+0.5+TA</t>
+          <t>Blok A &amp; B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2325,7 +2324,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2340,12 +2339,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>852</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Partially Furnished</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2370,32 +2369,32 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>MRT Bandar Tun Hussein Onn | AEON Big Bandar Tun Hussein Onn | AEON Cheras Selatan | SMK Bandar Tun Hussein Onn 2 | Cheras-Kajang Expressway</t>
+          <t>KTM UKM (~500m) | UKM Bangi (~2km) | Hentian Kajang (~2km) | MRT Kajang (~5km)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>/images/unitpic/pangsapuriwajaEX/pic1.jpg</t>
+          <t>/images/unitpic/apartmenttamantropikaNS/pic1.jpg</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>pangsapuriwajaEX</t>
+          <t>apartmenttamantropikaNS</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Pangsapuri Waja, Taman Tun Perak. Price: RM1100. Ref: EX</t>
+          <t>Hi Hani, I'm interested in the unit rental at Apartment Taman Tropika, Sungai Tangkas. Price: RM950. Ref: NS</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z13" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31792</t>
+          <t>https://t.me/rumahsewajualbelikldanselangor/13689</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2405,7 +2404,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2432,22 +2431,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ampang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Taman Dagang</t>
+          <t>Bukit Bintang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Metro Villa Apartment</t>
+          <t>City Gardens Condominium</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2457,12 +2456,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ground Floor | Facing Main Road | Deposit: 2+1+0.5+TA</t>
+          <t>Level 1 | Low Density (4 Units per Floor)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2492,7 +2491,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2502,7 +2501,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2522,42 +2521,42 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>LRT Cahaya | LRT Cempaka | Cahaya Dagang | Hospital Ampang | MRR2 Highway</t>
+          <t>Raja Chulan Monorail Station | MRT Bukit Bintang | Pavilion Kuala Lumpur | Suria KLCC | Prince Court Medical Centre</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>/images/unitpic/metrovillaapartmentEX/pic1.jpg</t>
+          <t>/images/unitpic/citygardenscondominiumNS/pic1.jpg</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>metrovillaapartmentEX</t>
+          <t>citygardenscondominiumNS</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Metro Villa Apartment, Taman Dagang. Price: RM1500. Ref: EX</t>
+          <t>Hi Hani, I'm interested in the unit rental at City Gardens Condominium, Bukit Bintang. Price: RM2800. Ref: NS</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z14" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31800</t>
+          <t>https://t.me/rumahsewajualbelikldanselangor/13701</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2584,37 +2583,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sepang/Dengkil/Banting</t>
+          <t>Puncak Alam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bandar Mahkota Banting</t>
+          <t>Puncak Alam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2 Storey Terrace Bandar Mahkota Banting</t>
+          <t>2 Storey Semi-D Cluster Puncak Alam</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Family Preferred</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Open to All Races | Master Bedroom Balcony | Tile Flooring | Fans &amp; Lights Provided | Viewing After Office Hours or Weekends</t>
+          <t>Cluster Semi-D | End Lot | Land Area 2000 sqft | Kitchen Cabinet Included</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2644,7 +2643,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2654,7 +2653,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Semi D</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2674,32 +2673,32 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Econsave Banting | Hospital Banting | West Coast Expressway (WCE) | SKVE Highway</t>
+          <t>Hospital Puncak Alam | UiTM Puncak Alam | Lotus's Puncak Alam | LATAR Expressway | GUTHRIE Corridor Expressway</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>/images/unitpic/2storeyterracebandarmahkotabantingNS/pic1.jpg</t>
+          <t>/images/unitpic/2storeysemidclusterpuncakalamNS/pic1.jpg</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2storeyterracebandarmahkotabantingNS</t>
+          <t>2storeysemidclusterpuncakalamNS</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at 2 Storey Terrace Bandar Mahkota Banting, Bandar Mahkota Banting. Price: RM1000. Ref: NS</t>
+          <t>Hi Hani, I'm interested in the unit rental at 2 Storey Semi-D Cluster Puncak Alam, Puncak Alam. Price: RM1400. Ref: NS</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z15" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/rumahsewajualbelikldanselangor/13582</t>
+          <t>https://t.me/rumahsewajualbelikldanselangor/13712</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2736,37 +2735,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cheras</t>
+          <t>Petaling Jaya / Damansara</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taman Connaught</t>
+          <t>Kelana Jaya</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Puncak Banyan Condominium</t>
+          <t>Kelana Sentral</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Malaysian Only</t>
+          <t>Professional/Family Preferred</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Level 3 | Beds &amp; Wardrobes in All Rooms | Washing Machine &amp; Fridge | Water Heaters in All Bathrooms</t>
+          <t>Level 9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2786,7 +2785,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2796,12 +2795,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fully Furnished</t>
+          <t>Partially Furnished</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2826,32 +2825,32 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>MRT Taman Connaught | IKON Connaught | Cheras LeisureMall | UCSI University | MRR2 Highway</t>
+          <t>LRT Kelana Jaya | Paradigm Mall | Kelana Mall | Kelana Jaya Medical Centre | LDP Highway</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>/images/unitpic/puncakbanyancondominiumADL/pic1.jpg</t>
+          <t>/images/unitpic/kelanasentralFPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>puncakbanyancondominiumADL</t>
+          <t>kelanasentralFPR</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Puncak Banyan Condominium, Taman Connaught. Price: RM2000. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at Kelana Sentral, Kelana Jaya. Price: RM1450. Ref: FPR</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z16" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14183</t>
+          <t>https://t.me/fathurpropertyrental/31239</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2861,7 +2860,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2888,37 +2887,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taman Wahyu</t>
+          <t>Setia Alam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eco Sky Residence</t>
+          <t>D'Sini Residence</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chinese Only</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Aurora Tower | Air-Conditioners | Washing Machine &amp; Fridge | Queen Bed &amp; Study Table</t>
+          <t>Level 23 | Brand New Unit</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2933,7 +2932,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2948,7 +2947,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2978,42 +2977,42 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>KTM Taman Wahyu | Selayang Mall | AEON Metro Prima | Hospital Selayang | DUKE Highway</t>
+          <t>Setia City Mall | Lotus's Setia Alam | Tenby Schools Setia Eco Park | NKVE | DASH Highway</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>/images/unitpic/ecoskyresidenceADL/pic1.jpg</t>
+          <t>/images/unitpic/dsiniresidenceFPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ecoskyresidenceADL</t>
+          <t>dsiniresidenceFPR</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Eco Sky Residence, Taman Wahyu. Price: RM3000. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at D'Sini Residence, Setia Alam. Price: RM2800. Ref: FPR</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z17" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14192</t>
+          <t>https://t.me/fathurpropertyrental/31248</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Immediate</t>
+          <t>Nov-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3040,37 +3039,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ampang</t>
+          <t>Bangi/Kajang</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pandan Mewah</t>
+          <t>Bandar Sungai Long</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hatta Square Apartment</t>
+          <t>Sutera Pines</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Family/Professional Preferred</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Level 3 | Open to Locals &amp; Foreigners | Water Heater</t>
+          <t>Corner Unit | Block B Level 10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3085,7 +3084,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3100,17 +3099,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3130,32 +3129,32 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>LRT Cahaya | LRT Pandan Indah | Paragon Point Shopping Complex | Hospital Ampang | MRR2 Highway</t>
+          <t>BMC Mall | UTAR Sungai Long Campus | Sungai Long Medical Centre | SILK Highway | LEKAS Highway</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>/images/unitpic/hattasquareapartmentADL/pic1.jpg</t>
+          <t>/images/unitpic/suterapinesFPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>hattasquareapartmentADL</t>
+          <t>suterapinesFPR</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Hatta Square Apartment, Pandan Mewah. Price: RM1500. Ref: ADL</t>
+          <t>Hi Hani, I'm interested in the unit rental at Sutera Pines, Bandar Sungai Long. Price: RM1800. Ref: FPR</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z18" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/adiblisting/14206</t>
+          <t>https://t.me/fathurpropertyrental/31257</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3165,7 +3164,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>ADL</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3192,37 +3191,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bangi/Kajang</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bangi Avenue</t>
+          <t>Taman Sri Sentosa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Residensi Adelia 3</t>
+          <t>Riverville Residence</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Local Preferred</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Level 24 | Balcony</t>
+          <t>Block B Level 10 | Big Unit | Balcony</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3247,17 +3246,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Fully Furnished</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3282,42 +3281,42 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>KTM Bangi | Bangi Wonderland | Pasaraya CS | UKM | KPTM</t>
+          <t>Pearl Point Shopping Gallery | Bloomsvale Shopping Mall | Mid Valley Megamall | Taman Desa Medical Centre | NPE Highway</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>/images/unitpic/residensiadelia3EX/pic1.jpg</t>
+          <t>/images/unitpic/rivervilleresidenceFPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>residensiadelia3EX</t>
+          <t>rivervilleresidenceFPR</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Residensi Adelia 3, Bangi Avenue. Price: RM1600. Ref: EX</t>
+          <t>Hi Hani, I'm interested in the unit rental at Riverville Residence, Taman Sri Sentosa. Price: RM2400. Ref: FPR</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z19" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31822</t>
+          <t>https://t.me/fathurpropertyrental/31271</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Dec-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3344,22 +3343,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Semenyih</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bandar Tasik Selatan</t>
+          <t>Sri Tanjung Kesuma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Residensi Sateria</t>
+          <t>JRK Senesta</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3369,12 +3368,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Level 45 | Block B</t>
+          <t>Level 5 | Basic Unit | Price Reduced from RM1300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3389,12 +3388,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3404,17 +3403,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Partially Furnished</t>
+          <t>Unfurnished</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3434,42 +3433,42 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Bandar Tasik Selatan LRT/KTM/KLIA Transit Station | Terminal Bersepadu Selatan (TBS) | Mid Valley Megamall | Hospital Kuala Lumpur | BESRAYA Highway</t>
+          <t>Ecohill Walk | Lotus's Semenyih | University of Nottingham Malaysia | LEKAS Highway | SILK Highway</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>/images/unitpic/residensisateriaEX/pic1.jpg</t>
+          <t>/images/unitpic/jrksenestaFPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>residensisateriaEX</t>
+          <t>jrksenestaFPR</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Residensi Sateria, Bandar Tasik Selatan. Price: RM1400. Ref: EX</t>
+          <t>Hi Hani, I'm interested in the unit rental at JRK Senesta, Sri Tanjung Kesuma. Price: RM1200. Ref: FPR</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z20" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31833</t>
+          <t>https://t.me/fathurpropertyrental/31311</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3496,37 +3495,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sentul</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jalan Sentul Pasar</t>
+          <t>Segambut</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sky Awani Residensi 1</t>
+          <t>Duta Park Residence</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Single/Couple Preferred | No Middle East, China &amp; African Tenants</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Level 28 | Batu Caves &amp; Sunrise View</t>
+          <t>Tower A Level 18 | Renovated | Balcony | Washer &amp; Dryer</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3556,7 +3555,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>957</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3586,42 +3585,42 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>MRT Jalan Ipoh | Sentul Boulevard | Tesco Sentul | DUKE Expressway</t>
+          <t>MRT Sentul West Station | LRT PWTC Station | Sunway Putra Mall | Hospital Kuala Lumpur | DUKE Highway</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>/images/unitpic/skyawaniresidensi1EX2/pic1.jpg</t>
+          <t>/images/unitpic/dutaparkresidenceFPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>skyawaniresidensi1EX2</t>
+          <t>dutaparkresidenceFPR</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Sky Awani Residensi 1, Jalan Sentul Pasar. Price: RM1900. Ref: EX</t>
+          <t>Hi Hani, I'm interested in the unit rental at Duta Park Residence, Segambut. Price: RM3600. Ref: FPR</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z21" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31846</t>
+          <t>https://t.me/fathurpropertyrental/31323</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1/11/2026</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3653,17 +3652,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sentul</t>
+          <t>Shah Alam</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jalan Sentul Pasar</t>
+          <t>Alam Impian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sky Awani Residensi 1</t>
+          <t>Pangsapuri Tun Teja 1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3673,12 +3672,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Level 28 | Batu Caves &amp; Sunrise View</t>
+          <t>Level 13 | Built-in Wardrobe, Shoe Cabinet &amp; Kitchen Cabinet</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3693,7 +3692,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3708,17 +3707,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fully Furnished</t>
+          <t>Partially Furnished</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3738,42 +3737,42 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>MRT Jalan Ipoh | Sentul Boulevard | Tesco Sentul | DUKE Expressway</t>
+          <t>Taman Tasik Alam Impian | AEON Big Seksyen 20 | Columbia Asia Hospital Bukit Rimau | KPJ Selangor Specialist Hospital | LKSA Highway</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>/images/unitpic/skyawaniresidensi1EX2/pic1.jpg</t>
+          <t>/images/unitpic/pangsapuritunteja1FPR/pic1.jpg</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>skyawaniresidensi1EX2</t>
+          <t>pangsapuritunteja1FPR</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Sky Awani Residensi 1, Jalan Sentul Pasar. Price: RM1900. Ref: EX</t>
+          <t>Hi Hani, I'm interested in the unit rental at Pangsapuri Tun Teja 1, Alam Impian. Price: RM1300. Ref: FPR</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z22" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/RumahSewaKLSlgrBelowRM2000/31846</t>
+          <t>https://t.me/fathurpropertyrental/31372</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1/11/2026</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>EX</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3800,22 +3799,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Klang</t>
+          <t>Seri Kembangan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kapar</t>
+          <t>Taman Lestari Perdana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapar Setia 3</t>
+          <t>Prestige Residence</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3825,12 +3824,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Kitchen Tabletop | Covered Car Porch</t>
+          <t>Level 8 | Rent Negotiable | Deposit 2+1+0.5+TA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3845,12 +3844,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3860,7 +3859,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3870,7 +3869,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3890,42 +3889,42 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>WCE (West Coast Expressway) | Pekan Kapar</t>
+          <t>MRT Putra Permai | AEON Mall Taman Equine | Hospital Serdang | MEX Highway | SKVE</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>/images/unitpic/kaparsetia3NS/pic1.jpg</t>
+          <t>/images/unitpic/prestigeresidenceBLA/pic1.jpg</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>kaparsetia3NS</t>
+          <t>prestigeresidenceBLA</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Hi Hani, I'm interested in the unit rental at Kapar Setia 3, Kapar. Price: RM1200. Ref: NS</t>
+          <t>Hi Hani, I'm interested in the unit rental at Prestige Residence, Taman Lestari Perdana. Price: RM1500. Ref: BLA</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="Z23" s="1" t="inlineStr">
         <is>
-          <t>https://t.me/rumahsewajualbelikldanselangor/13593</t>
+          <t>https://t.me/Bala_listing/1946</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nov-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>BLA</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3934,2141 +3933,13 @@
         </is>
       </c>
       <c r="AD23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Sepang/Dengkil/Banting</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Kota Warisan</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Jalan Warisan Indah</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Re-open | Rent Nett | Security | Playground</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Partially Furnished</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Terrace</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Salak Tinggi ERL Station | KIP Mall Kota Warisan | Mitsui Outlet Park | Xiamen University | ELITE Highway</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>/images/unitpic/jalanwarisanindahNS/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>jalanwarisanindahNS</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Jalan Warisan Indah, Kota Warisan. Price: RM1800. Ref: NS</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z24" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/rumahsewajualbelikldanselangor/13602</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Jan-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bangi/Kajang</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Kajang 2</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Residensi Jade</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Level 22 | 2 New Aircond &amp; 3 New Fans</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Unfurnished</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>KTM Kajang 2</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>/images/unitpic/residensijadeNS/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>residensijadeNS</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Residensi Jade, Kajang 2. Price: RM1600. Ref: NS</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z25" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/rumahsewajualbelikldanselangor/13614</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Desa Petaling</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Widuri Impian Condominium</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Price Negotiable | Covered Parking</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Partially Furnished</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Condominium</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>LRT/KTM Bandar Tasik Selatan | Terminal Bersepadu Selatan (TBS) | Giant Desa Petaling | KESAS Highway | MEX Highway</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>/images/unitpic/widuriimpiancondominiumNS/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>widuriimpiancondominiumNS</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Widuri Impian Condominium, Desa Petaling. Price: RM1650. Ref: NS</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z26" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/rumahsewajualbelikldanselangor/13625</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Sepang/Dengkil/Banting</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Salak Perdana</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Acacia Residences</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Malaysian Only | Malay Only | Working Adults Only</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Fully Furnished</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Condominium</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Salak Tinggi ERL Station | KIP Mall Kota Warisan | Xiamen University Malaysia | ELITE Highway</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>/images/unitpic/acaciaresidencesNS/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>acaciaresidencesNS</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Acacia Residences, Salak Perdana. Price: RM1700. Ref: NS</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z27" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/rumahsewajualbelikldanselangor/13638</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Brickfields</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Riveria City</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Block A Level 20 | Medium Floor</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Fully Furnished</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Studio</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>KL Sentral | NU Sentral | Mid Valley Megamall | Pantai Hospital Kuala Lumpur | Universiti Malaya</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>/images/unitpic/riveriacityFPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>riveriacityFPR</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Riveria City, Brickfields. Price: RM1700. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z28" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/31182</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Mid November 2026</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Kepong</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Taman KIP</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Suria Kipark Damansara</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Block A Level 02 | Low Floor</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Fully Furnished</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>MRT Sri Damansara Barat | Plaza Ativo | Decathlon Bandar Sri Damansara | Kepong Metropolitan Park | LDP Highway</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>/images/unitpic/suriakiparkdamansaraFPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>suriakiparkdamansaraFPR</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Suria Kipark Damansara, Taman KIP. Price: RM1650. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z29" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/31191</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Petaling Jaya / Damansara</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Damansara Perdana</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Empire Damansara</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No Pets Owner</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>SOHO 1 Block C Level 09 | Low Floor | Fully Renovated</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Fully Furnished</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>SOHO</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>MRT Mutiara Damansara | The Curve | IKEA Damansara | KPJ Damansara Specialist Hospital 2 | LDP Highway</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>/images/unitpic/empiredamansaraFPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>empiredamansaraFPR</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Empire Damansara, Damansara Perdana. Price: RM1850. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z30" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/31203</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bukit Jalil</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Taman LTAT</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Taman LTAT Apartment</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Local Preferred | Family Preferred</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Level 06 | Low Floor | Balcony | Newly Painted</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Unfurnished</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>LRT Alam Sutera | Pavilion Bukit Jalil | Technology Park Malaysia | Bukit Jalil Highway</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>/images/unitpic/tamanltatapartmentFPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>tamanltatapartmentFPR</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Taman LTAT Apartment, Bukit Jalil. Price: RM1300. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z31" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/31214</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Puchong</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Jalan Millenia</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Vista Millennium Condominium</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Local Only</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Level 02 | Low Floor | Big Unit</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Partially Furnished</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Condominium</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>LRT Puchong Prima | LRT Puchong Perdana | OTK Supermarket Puchong Prima | LDP Highway | KESAS Highway</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>/images/unitpic/vistamillenniumcondominiumFPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>vistamillenniumcondominiumFPR</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Vista Millennium Condominium, Jalan Millenia. Price: RM1350. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z32" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/31018</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Nov-26</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Bukit Jalil</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Bukit Jalil</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Apartment Seri Ceria 2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Corner Unit | Block H Level 01 | Low Floor | Open Parking</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Unfurnished</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Pavilion Bukit Jalil | Columbia Asia Hospital Bukit Jalil | Technology Park Malaysia | Axiata Arena | MEX Highway</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>/images/unitpic/apartmentsericeria2FPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>apartmentsericeria2FPR</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Apartment Seri Ceria 2, Bukit Jalil. Price: RM1000. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z33" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/30803</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bangi/Kajang</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Bandar Baru Bangi</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Evo SOHO Suites</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>SOHO-style | Corner Unit | Level 11 | Medium Floor</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Fully Furnished</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Duplex</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Evo Shopping Mall | KIP Mall Bangi | Hospital Islam Az-Zahrah | Kompleks PKNS Bangi | LEKAS Highway</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>/images/unitpic/evosohosuitesFPR/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>evosohosuitesFPR</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Evo SOHO Suites, Bandar Baru Bangi. Price: RM3100. Ref: FPR</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z34" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/fathurpropertyrental/30610</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Dec-26</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>FPR</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Bandar Tasik Selatan</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Residensi Sateria</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Malay Only</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Level 45 | Block B</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Partially Furnished</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Bandar Tasik Selatan LRT/KTM/KLIA Transit Station | Terminal Bersepadu Selatan (TBS) | Mid Valley Megamall | Hospital Kuala Lumpur | BESRAYA Highway</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>/images/unitpic/residensisateriaEX/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>residensisateriaEX</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Residensi Sateria, Bandar Tasik Selatan. Price: RM1400. Ref: ADL</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z35" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/adiblisting/14323</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>ADL</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Selayang</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Taman Amansiara</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Amansiara Townhouse</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Kitchen Top | Open Parking</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Unfurnished</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Townhouse</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Selayang Mall | Lotus's Selayang | NSK Trade City Selayang | Hospital Selayang | MRR2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>/images/unitpic/amansiaratownhouseADL/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>amansiaratownhouseADL</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at Amansiara Townhouse, Taman Amansiara. Price: RM1200. Ref: ADL</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z36" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/adiblisting/14334</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>ADL</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>rental</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Shah Alam</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Seksyen U10</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2 Storey Terrace Alam Budiman</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Long-term Tenant | Family Preferred</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Land 22' x 70' | 3 Aircond | Deposit 2+1+0.5 (Total RM6650 excl TA)</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Partially Furnished</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Terrace</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Setia City Mall | Columbia Asia Hospital Setia Alam | UiTM Puncak Perdana | GCE | NKVE</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>/images/unitpic/2storeyterracealambudimanMMN/pic1.jpg</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2storeyterracealambudimanMMN</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Hi Hani, I'm interested in the unit rental at 2 Storey Terrace Alam Budiman, Seksyen U10. Price: RM1900. Ref: MMN</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="Z37" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/AniListings/4248</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>MMN</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE37"/>
+  <autoFilter ref="A1:AD23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId2"/>
@@ -6076,8 +3947,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z7" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z8" r:id="rId11"/>
@@ -6096,20 +3967,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z21" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z22" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z23" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z24" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z25" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z26" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z27" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z28" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z29" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z30" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z31" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z32" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z33" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z34" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z35" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z36" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z37" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
